--- a/data/numeric/input/old_data_41/门诊信息表_脱敏.xlsx
+++ b/data/numeric/input/old_data_41/门诊信息表_脱敏.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\panzheng1\Documents\work\files\tmp\20260205\graph_data\输入数据\old_data_41\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D2BCA8-EBCF-4690-8BE4-09A9C22DC028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="14725" activeTab="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -94,9 +100,6 @@
     <t>41</t>
   </si>
   <si>
-    <t>抖音</t>
-  </si>
-  <si>
     <t>白内障门诊</t>
   </si>
   <si>
@@ -208,9 +211,6 @@
     <t>人员13</t>
   </si>
   <si>
-    <t>美团</t>
-  </si>
-  <si>
     <t>医生11</t>
   </si>
   <si>
@@ -536,373 +536,36 @@
   </si>
   <si>
     <t>合计</t>
+  </si>
+  <si>
+    <t>来源A</t>
+  </si>
+  <si>
+    <t>来源B</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -910,310 +573,24 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1498,16 +875,16 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I41"/>
-  <sheetFormatPr defaultColWidth="8.82882882882883" defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="8" max="8" width="17.3333333333333" customWidth="1"/>
+    <col min="8" max="8" width="17.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1585,16 +962,16 @@
         <v>19</v>
       </c>
       <c r="F3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>21</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>22</v>
-      </c>
-      <c r="I3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1605,25 +982,25 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G4" t="s">
         <v>25</v>
       </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>26</v>
       </c>
-      <c r="H4" t="s">
-        <v>27</v>
-      </c>
       <c r="I4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1634,22 +1011,22 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" t="s">
         <v>30</v>
-      </c>
-      <c r="H5" t="s">
-        <v>31</v>
       </c>
       <c r="I5" t="s">
         <v>17</v>
@@ -1663,22 +1040,22 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
         <v>32</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>33</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>34</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>35</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>36</v>
-      </c>
-      <c r="H6" t="s">
-        <v>37</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -1692,22 +1069,22 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -1721,22 +1098,22 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
         <v>40</v>
       </c>
-      <c r="D8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" t="s">
-        <v>41</v>
-      </c>
       <c r="F8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" t="s">
         <v>35</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>36</v>
-      </c>
-      <c r="H8" t="s">
-        <v>37</v>
       </c>
       <c r="I8" t="s">
         <v>17</v>
@@ -1750,25 +1127,25 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
       <c r="E9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" t="s">
+        <v>166</v>
+      </c>
+      <c r="G9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" t="s">
         <v>43</v>
       </c>
-      <c r="F9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" t="s">
-        <v>44</v>
-      </c>
       <c r="I9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1779,22 +1156,22 @@
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" t="s">
         <v>46</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>47</v>
-      </c>
-      <c r="H10" t="s">
-        <v>48</v>
       </c>
       <c r="I10" t="s">
         <v>17</v>
@@ -1808,22 +1185,22 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" t="s">
         <v>50</v>
-      </c>
-      <c r="F11" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" t="s">
-        <v>51</v>
       </c>
       <c r="I11" t="s">
         <v>17</v>
@@ -1837,22 +1214,22 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s">
         <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I12" t="s">
         <v>17</v>
@@ -1866,22 +1243,22 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" t="s">
         <v>54</v>
       </c>
-      <c r="D13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" t="s">
         <v>55</v>
-      </c>
-      <c r="F13" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" t="s">
-        <v>56</v>
       </c>
       <c r="I13" t="s">
         <v>17</v>
@@ -1895,7 +1272,7 @@
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
@@ -1904,16 +1281,16 @@
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>167</v>
       </c>
       <c r="G14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1924,22 +1301,22 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I15" t="s">
         <v>17</v>
@@ -1953,22 +1330,22 @@
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I16" t="s">
         <v>17</v>
@@ -1982,22 +1359,22 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I17" t="s">
         <v>17</v>
@@ -2011,22 +1388,22 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" t="s">
         <v>67</v>
-      </c>
-      <c r="D18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" t="s">
-        <v>68</v>
-      </c>
-      <c r="F18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G18" t="s">
-        <v>30</v>
-      </c>
-      <c r="H18" t="s">
-        <v>69</v>
       </c>
       <c r="I18" t="s">
         <v>17</v>
@@ -2040,22 +1417,22 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I19" t="s">
         <v>17</v>
@@ -2069,22 +1446,22 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E20" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I20" t="s">
         <v>17</v>
@@ -2098,22 +1475,22 @@
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s">
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I21" t="s">
         <v>17</v>
@@ -2127,22 +1504,22 @@
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E22" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I22" t="s">
         <v>17</v>
@@ -2156,22 +1533,22 @@
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E23" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H23" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I23" t="s">
         <v>17</v>
@@ -2185,22 +1562,22 @@
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I24" t="s">
         <v>17</v>
@@ -2214,22 +1591,22 @@
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D25" t="s">
         <v>12</v>
       </c>
       <c r="E25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" t="s">
+        <v>45</v>
+      </c>
+      <c r="G25" t="s">
         <v>25</v>
       </c>
-      <c r="F25" t="s">
-        <v>46</v>
-      </c>
-      <c r="G25" t="s">
-        <v>26</v>
-      </c>
       <c r="H25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I25" t="s">
         <v>17</v>
@@ -2243,22 +1620,22 @@
         <v>10</v>
       </c>
       <c r="C26" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" t="s">
+        <v>82</v>
+      </c>
+      <c r="F26" t="s">
+        <v>34</v>
+      </c>
+      <c r="G26" t="s">
+        <v>46</v>
+      </c>
+      <c r="H26" t="s">
         <v>83</v>
-      </c>
-      <c r="D26" t="s">
-        <v>33</v>
-      </c>
-      <c r="E26" t="s">
-        <v>84</v>
-      </c>
-      <c r="F26" t="s">
-        <v>35</v>
-      </c>
-      <c r="G26" t="s">
-        <v>47</v>
-      </c>
-      <c r="H26" t="s">
-        <v>85</v>
       </c>
       <c r="I26" t="s">
         <v>17</v>
@@ -2272,22 +1649,22 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D27" t="s">
         <v>12</v>
       </c>
       <c r="E27" t="s">
+        <v>85</v>
+      </c>
+      <c r="F27" t="s">
+        <v>86</v>
+      </c>
+      <c r="G27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H27" t="s">
         <v>87</v>
-      </c>
-      <c r="F27" t="s">
-        <v>88</v>
-      </c>
-      <c r="G27" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" t="s">
-        <v>89</v>
       </c>
       <c r="I27" t="s">
         <v>17</v>
@@ -2301,22 +1678,22 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D28" t="s">
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F28" t="s">
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H28" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I28" t="s">
         <v>17</v>
@@ -2330,22 +1707,22 @@
         <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s">
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H29" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I29" t="s">
         <v>17</v>
@@ -2359,25 +1736,25 @@
         <v>10</v>
       </c>
       <c r="C30" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" t="s">
+        <v>42</v>
+      </c>
+      <c r="F30" t="s">
+        <v>167</v>
+      </c>
+      <c r="G30" t="s">
+        <v>95</v>
+      </c>
+      <c r="H30" t="s">
         <v>96</v>
       </c>
-      <c r="D30" t="s">
-        <v>33</v>
-      </c>
-      <c r="E30" t="s">
-        <v>43</v>
-      </c>
-      <c r="F30" t="s">
-        <v>58</v>
-      </c>
-      <c r="G30" t="s">
-        <v>97</v>
-      </c>
-      <c r="H30" t="s">
-        <v>98</v>
-      </c>
       <c r="I30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -2388,22 +1765,22 @@
         <v>10</v>
       </c>
       <c r="C31" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" t="s">
+        <v>98</v>
+      </c>
+      <c r="F31" t="s">
+        <v>45</v>
+      </c>
+      <c r="G31" t="s">
+        <v>25</v>
+      </c>
+      <c r="H31" t="s">
         <v>99</v>
-      </c>
-      <c r="D31" t="s">
-        <v>33</v>
-      </c>
-      <c r="E31" t="s">
-        <v>100</v>
-      </c>
-      <c r="F31" t="s">
-        <v>46</v>
-      </c>
-      <c r="G31" t="s">
-        <v>26</v>
-      </c>
-      <c r="H31" t="s">
-        <v>101</v>
       </c>
       <c r="I31" t="s">
         <v>17</v>
@@ -2417,22 +1794,22 @@
         <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E32" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H32" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I32" t="s">
         <v>17</v>
@@ -2446,22 +1823,22 @@
         <v>10</v>
       </c>
       <c r="C33" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D33" t="s">
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H33" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I33" t="s">
         <v>17</v>
@@ -2475,22 +1852,22 @@
         <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D34" t="s">
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H34" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I34" t="s">
         <v>17</v>
@@ -2504,25 +1881,25 @@
         <v>10</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D35" t="s">
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F35" t="s">
-        <v>58</v>
+        <v>167</v>
       </c>
       <c r="G35" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -2533,22 +1910,22 @@
         <v>10</v>
       </c>
       <c r="C36" t="s">
+        <v>110</v>
+      </c>
+      <c r="D36" t="s">
+        <v>32</v>
+      </c>
+      <c r="E36" t="s">
+        <v>111</v>
+      </c>
+      <c r="F36" t="s">
+        <v>34</v>
+      </c>
+      <c r="G36" t="s">
+        <v>46</v>
+      </c>
+      <c r="H36" t="s">
         <v>112</v>
-      </c>
-      <c r="D36" t="s">
-        <v>33</v>
-      </c>
-      <c r="E36" t="s">
-        <v>113</v>
-      </c>
-      <c r="F36" t="s">
-        <v>35</v>
-      </c>
-      <c r="G36" t="s">
-        <v>47</v>
-      </c>
-      <c r="H36" t="s">
-        <v>114</v>
       </c>
       <c r="I36" t="s">
         <v>17</v>
@@ -2562,25 +1939,25 @@
         <v>10</v>
       </c>
       <c r="C37" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D37" t="s">
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F37" t="s">
-        <v>58</v>
+        <v>167</v>
       </c>
       <c r="G37" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H37" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -2591,22 +1968,22 @@
         <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D38" t="s">
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H38" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I38" t="s">
         <v>17</v>
@@ -2620,22 +1997,22 @@
         <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D39" t="s">
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G39" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I39" t="s">
         <v>17</v>
@@ -2649,22 +2026,22 @@
         <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E40" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H40" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I40" t="s">
         <v>17</v>
@@ -2678,41 +2055,37 @@
         <v>10</v>
       </c>
       <c r="C41" t="s">
+        <v>124</v>
+      </c>
+      <c r="D41" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41" t="s">
+        <v>125</v>
+      </c>
+      <c r="F41" t="s">
+        <v>34</v>
+      </c>
+      <c r="G41" t="s">
+        <v>46</v>
+      </c>
+      <c r="H41" t="s">
         <v>126</v>
       </c>
-      <c r="D41" t="s">
-        <v>33</v>
-      </c>
-      <c r="E41" t="s">
-        <v>127</v>
-      </c>
-      <c r="F41" t="s">
-        <v>35</v>
-      </c>
-      <c r="G41" t="s">
-        <v>47</v>
-      </c>
-      <c r="H41" t="s">
-        <v>128</v>
-      </c>
       <c r="I41" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I41" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:I41" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q41"/>
-  <sheetFormatPr defaultColWidth="8.82882882882883" defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" t="s">
@@ -2722,16 +2095,16 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I1" t="s">
+        <v>128</v>
+      </c>
+      <c r="L1" t="s">
         <v>129</v>
       </c>
-      <c r="I1" t="s">
+      <c r="O1" t="s">
         <v>130</v>
-      </c>
-      <c r="L1" t="s">
-        <v>131</v>
-      </c>
-      <c r="O1" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -2739,43 +2112,43 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H2" t="s">
         <v>132</v>
       </c>
-      <c r="H2" t="s">
-        <v>134</v>
-      </c>
       <c r="I2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J2" t="s">
+        <v>130</v>
+      </c>
+      <c r="K2" t="s">
         <v>132</v>
       </c>
-      <c r="K2" t="s">
-        <v>134</v>
-      </c>
       <c r="L2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="M2" t="s">
+        <v>130</v>
+      </c>
+      <c r="N2" t="s">
         <v>132</v>
       </c>
-      <c r="N2" t="s">
-        <v>134</v>
-      </c>
       <c r="O2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="P2" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q2" t="s">
         <v>132</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -2783,10 +2156,10 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F3">
         <v>10</v>
@@ -2830,10 +2203,10 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F4">
         <v>20</v>
@@ -2877,10 +2250,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F5">
         <v>30</v>
@@ -2924,10 +2297,10 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F6">
         <v>98</v>
@@ -2971,10 +2344,10 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F7">
         <v>96</v>
@@ -3018,7 +2391,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -3026,7 +2399,7 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -3034,7 +2407,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -3042,7 +2415,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -3050,7 +2423,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -3058,7 +2431,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -3066,7 +2439,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -3074,7 +2447,7 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -3082,7 +2455,7 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -3090,7 +2463,7 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -3098,7 +2471,7 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -3106,13 +2479,13 @@
         <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F19" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G19" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -3120,10 +2493,10 @@
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F20">
         <v>35</v>
@@ -3137,10 +2510,10 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F21">
         <v>46</v>
@@ -3154,10 +2527,10 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E22" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F22">
         <v>40</v>
@@ -3171,10 +2544,10 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F23">
         <v>95</v>
@@ -3188,10 +2561,10 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E24" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F24">
         <v>79</v>
@@ -3205,7 +2578,7 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -3213,7 +2586,7 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3221,7 +2594,7 @@
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -3229,7 +2602,7 @@
         <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -3237,7 +2610,7 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -3245,7 +2618,7 @@
         <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3253,7 +2626,7 @@
         <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3261,129 +2634,127 @@
         <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B33" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B34" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B35" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B36" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B39" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B40" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B12:M26"/>
-  <sheetFormatPr defaultColWidth="8.82882882882883" defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="12" spans="2:13">
       <c r="B12" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" t="s">
+        <v>145</v>
+      </c>
+      <c r="D12" t="s">
         <v>146</v>
       </c>
-      <c r="C12" t="s">
+      <c r="E12" t="s">
         <v>147</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>148</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
         <v>149</v>
       </c>
-      <c r="F12" t="s">
+      <c r="H12" t="s">
         <v>150</v>
       </c>
-      <c r="G12" t="s">
+      <c r="I12" t="s">
         <v>151</v>
       </c>
-      <c r="H12" t="s">
+      <c r="J12" t="s">
         <v>152</v>
       </c>
-      <c r="I12" t="s">
+      <c r="K12" t="s">
         <v>153</v>
       </c>
-      <c r="J12" t="s">
+      <c r="L12" t="s">
         <v>154</v>
       </c>
-      <c r="K12" t="s">
+      <c r="M12" t="s">
         <v>155</v>
-      </c>
-      <c r="L12" t="s">
-        <v>156</v>
-      </c>
-      <c r="M12" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="13" spans="2:13">
@@ -3429,30 +2800,30 @@
         <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E19" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F19" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I19" t="s">
         <v>8</v>
       </c>
       <c r="J19" t="s">
+        <v>156</v>
+      </c>
+      <c r="K19" t="s">
         <v>158</v>
       </c>
-      <c r="K19" t="s">
-        <v>160</v>
-      </c>
       <c r="L19" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="3:12">
       <c r="C20" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D20">
         <v>37</v>
@@ -3484,7 +2855,7 @@
     </row>
     <row r="21" spans="3:12">
       <c r="C21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D21">
         <v>36</v>
@@ -3516,7 +2887,7 @@
     </row>
     <row r="22" spans="3:12">
       <c r="C22" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D22">
         <v>30</v>
@@ -3548,7 +2919,7 @@
     </row>
     <row r="23" spans="3:12">
       <c r="C23" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D23">
         <v>11</v>
@@ -3580,7 +2951,7 @@
     </row>
     <row r="24" spans="3:12">
       <c r="C24" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D24">
         <v>22</v>
@@ -3612,7 +2983,7 @@
     </row>
     <row r="25" spans="3:12">
       <c r="C25" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D25">
         <v>33</v>
@@ -3644,7 +3015,7 @@
     </row>
     <row r="26" spans="3:12">
       <c r="C26" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D26">
         <v>43</v>
@@ -3676,7 +3047,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -3844,13 +3214,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A35E32D-7708-40F2-9F73-A33DA1FC19CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9070CC3E-AAD2-4759-B79F-2ACECD022EE3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B082FDFD-B69E-4C6F-B30B-E3C0619EE25E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7104A266-A956-4C48-BC5E-02A0DE182F1F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B2C6D85-2497-485D-8293-97C9E7AC164D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D5C6D08-39FA-4EDB-B1FB-CB5A91D257CF}"/>
 </file>